--- a/test-exports/sales-2020-01-01-to-2030-01-01.xlsx
+++ b/test-exports/sales-2020-01-01-to-2030-01-01.xlsx
@@ -758,142 +758,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="KusumExport1" displayName="KusumExport1" ref="A5:Z31" totalsRowShown="1" headerRowCount="1">
-  <autoFilter ref="A5:Z31">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-    <filterColumn colId="2" hiddenButton="1"/>
-    <filterColumn colId="3" hiddenButton="1"/>
-    <filterColumn colId="4" hiddenButton="1"/>
-    <filterColumn colId="5" hiddenButton="1"/>
-    <filterColumn colId="6" hiddenButton="1"/>
-    <filterColumn colId="7" hiddenButton="1"/>
-    <filterColumn colId="8" hiddenButton="1"/>
-    <filterColumn colId="9" hiddenButton="1"/>
-    <filterColumn colId="10" hiddenButton="1"/>
-    <filterColumn colId="11" hiddenButton="1"/>
-    <filterColumn colId="12" hiddenButton="1"/>
-    <filterColumn colId="13" hiddenButton="1"/>
-    <filterColumn colId="14" hiddenButton="1"/>
-    <filterColumn colId="15" hiddenButton="1"/>
-    <filterColumn colId="16" hiddenButton="1"/>
-    <filterColumn colId="17" hiddenButton="1"/>
-    <filterColumn colId="18" hiddenButton="1"/>
-    <filterColumn colId="19" hiddenButton="1"/>
-    <filterColumn colId="20" hiddenButton="1"/>
-    <filterColumn colId="21" hiddenButton="1"/>
-    <filterColumn colId="22" hiddenButton="1"/>
-    <filterColumn colId="23" hiddenButton="1"/>
-    <filterColumn colId="24" hiddenButton="1"/>
-    <filterColumn colId="25" hiddenButton="1"/>
-  </autoFilter>
-  <tableColumns count="26">
-    <tableColumn id="1" name="Invoice date" totalsRowLabel="Total"/>
-    <tableColumn id="2" name="Invoice no." totalsRowFunction="none"/>
-    <tableColumn id="3" name="Customer phone" totalsRowFunction="none"/>
-    <tableColumn id="4" name="Customer" totalsRowFunction="none"/>
-    <tableColumn id="5" name="PAN no." totalsRowFunction="none"/>
-    <tableColumn id="6" name="Items sold" totalsRowFunction="none"/>
-    <tableColumn id="7" name="Total weight (g)" totalsRowFunction="none"/>
-    <tableColumn id="8" name="Subtotal" totalsRowFunction="none"/>
-    <tableColumn id="9" name="Discount" totalsRowFunction="none"/>
-    <tableColumn id="10" name="Taxable value" totalsRowFunction="none"/>
-    <tableColumn id="11" name="CGST (%)" totalsRowFunction="none"/>
-    <tableColumn id="12" name="CGST amount" totalsRowFunction="none"/>
-    <tableColumn id="13" name="SGST (%)" totalsRowFunction="none"/>
-    <tableColumn id="14" name="SGST amount" totalsRowFunction="none"/>
-    <tableColumn id="15" name="Invoice total" totalsRowFunction="none"/>
-    <tableColumn id="16" name="URD adjustment" totalsRowFunction="none"/>
-    <tableColumn id="17" name="Net payable" totalsRowFunction="none"/>
-    <tableColumn id="18" name="Total paid" totalsRowFunction="none"/>
-    <tableColumn id="19" name="Cash paid" totalsRowFunction="none"/>
-    <tableColumn id="20" name="UPI paid" totalsRowFunction="none"/>
-    <tableColumn id="21" name="Card paid" totalsRowFunction="none"/>
-    <tableColumn id="22" name="Bank transfer paid" totalsRowFunction="none"/>
-    <tableColumn id="23" name="Other paid" totalsRowFunction="none"/>
-    <tableColumn id="24" name="Due balance" totalsRowFunction="none"/>
-    <tableColumn id="25" name="Payment method" totalsRowFunction="none"/>
-    <tableColumn id="26" name="Notes" totalsRowFunction="none"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" name="KusumExport2" displayName="KusumExport2" ref="A5:AF31" totalsRowShown="1" headerRowCount="1">
-  <autoFilter ref="A5:AF31">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-    <filterColumn colId="2" hiddenButton="1"/>
-    <filterColumn colId="3" hiddenButton="1"/>
-    <filterColumn colId="4" hiddenButton="1"/>
-    <filterColumn colId="5" hiddenButton="1"/>
-    <filterColumn colId="6" hiddenButton="1"/>
-    <filterColumn colId="7" hiddenButton="1"/>
-    <filterColumn colId="8" hiddenButton="1"/>
-    <filterColumn colId="9" hiddenButton="1"/>
-    <filterColumn colId="10" hiddenButton="1"/>
-    <filterColumn colId="11" hiddenButton="1"/>
-    <filterColumn colId="12" hiddenButton="1"/>
-    <filterColumn colId="13" hiddenButton="1"/>
-    <filterColumn colId="14" hiddenButton="1"/>
-    <filterColumn colId="15" hiddenButton="1"/>
-    <filterColumn colId="16" hiddenButton="1"/>
-    <filterColumn colId="17" hiddenButton="1"/>
-    <filterColumn colId="18" hiddenButton="1"/>
-    <filterColumn colId="19" hiddenButton="1"/>
-    <filterColumn colId="20" hiddenButton="1"/>
-    <filterColumn colId="21" hiddenButton="1"/>
-    <filterColumn colId="22" hiddenButton="1"/>
-    <filterColumn colId="23" hiddenButton="1"/>
-    <filterColumn colId="24" hiddenButton="1"/>
-    <filterColumn colId="25" hiddenButton="1"/>
-    <filterColumn colId="26" hiddenButton="1"/>
-    <filterColumn colId="27" hiddenButton="1"/>
-    <filterColumn colId="28" hiddenButton="1"/>
-    <filterColumn colId="29" hiddenButton="1"/>
-    <filterColumn colId="30" hiddenButton="1"/>
-    <filterColumn colId="31" hiddenButton="1"/>
-  </autoFilter>
-  <tableColumns count="32">
-    <tableColumn id="1" name="Invoice date" totalsRowLabel="Total"/>
-    <tableColumn id="2" name="Invoice no." totalsRowFunction="none"/>
-    <tableColumn id="3" name="Customer phone" totalsRowFunction="none"/>
-    <tableColumn id="4" name="Customer" totalsRowFunction="none"/>
-    <tableColumn id="5" name="PAN no." totalsRowFunction="none"/>
-    <tableColumn id="6" name="Barcode" totalsRowFunction="none"/>
-    <tableColumn id="7" name="Item name" totalsRowFunction="none"/>
-    <tableColumn id="8" name="Metal" totalsRowFunction="none"/>
-    <tableColumn id="9" name="Purity" totalsRowFunction="none"/>
-    <tableColumn id="10" name="HSN code" totalsRowFunction="none"/>
-    <tableColumn id="11" name="HUID" totalsRowFunction="none"/>
-    <tableColumn id="12" name="Qty" totalsRowFunction="none"/>
-    <tableColumn id="13" name="Gross wt. (g)" totalsRowFunction="none"/>
-    <tableColumn id="14" name="Weight (g)" totalsRowFunction="none"/>
-    <tableColumn id="15" name="Rate / g" totalsRowFunction="none"/>
-    <tableColumn id="16" name="Metal value" totalsRowFunction="none"/>
-    <tableColumn id="17" name="Making basis" totalsRowFunction="none"/>
-    <tableColumn id="18" name="Making value" totalsRowFunction="none"/>
-    <tableColumn id="19" name="Making amount" totalsRowFunction="none"/>
-    <tableColumn id="20" name="Taxable amount" totalsRowFunction="none"/>
-    <tableColumn id="21" name="GST rate (%)" totalsRowFunction="none"/>
-    <tableColumn id="22" name="Invoice total" totalsRowFunction="none"/>
-    <tableColumn id="23" name="URD adjustment" totalsRowFunction="none"/>
-    <tableColumn id="24" name="Total paid" totalsRowFunction="none"/>
-    <tableColumn id="25" name="Cash paid" totalsRowFunction="none"/>
-    <tableColumn id="26" name="UPI paid" totalsRowFunction="none"/>
-    <tableColumn id="27" name="Card paid" totalsRowFunction="none"/>
-    <tableColumn id="28" name="Bank transfer paid" totalsRowFunction="none"/>
-    <tableColumn id="29" name="Other paid" totalsRowFunction="none"/>
-    <tableColumn id="30" name="Due balance" totalsRowFunction="none"/>
-    <tableColumn id="31" name="Payment method" totalsRowFunction="none"/>
-    <tableColumn id="32" name="Notes" totalsRowFunction="none"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3454,9 +3318,6 @@
     <oddFooter>&amp;LKusum ERP&amp;CConfidential business register&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenFooter>&amp;LKusum ERP&amp;CConfidential business register&amp;RPage &amp;P of &amp;N</evenFooter>
   </headerFooter>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -6088,8 +5949,5 @@
     <oddFooter>&amp;LKusum ERP&amp;CConfidential business register&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenFooter>&amp;LKusum ERP&amp;CConfidential business register&amp;RPage &amp;P of &amp;N</evenFooter>
   </headerFooter>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>